--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260717.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>9,622,000</t>
+          <t>9,734,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -655,122 +655,122 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5,382,000</t>
+          <t>5,482,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,446,000</t>
+          <t>44,375,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>43,790,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10,846,000</t>
+          <t>32,516,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,501,000</t>
+          <t>11,037,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>14,524,000</t>
+          <t>19,101,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -787,254 +787,254 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,590,000</t>
+          <t>3,692,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,101,000</t>
+          <t>9,544,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>32,516,000</t>
+          <t>14,837,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>4,071,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,803,000</t>
+          <t>32,918,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>32,918,000</t>
+          <t>4,096,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>28,640,000</t>
+          <t>23,799,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>23,799,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,105,000</t>
+          <t>28,640,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>17,008,000</t>
+          <t>2,151,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>32,659,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>32,659,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>19,313,000</t>
+          <t>19,261,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,44 +1085,44 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>19,261,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>19,313,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1151,66 +1151,66 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>16,240,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5,983,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>5,983,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,206,000</t>
+          <t>2,250,291,463</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1298,29 +1298,29 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>13,206,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1349,132 +1349,132 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,334,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>8,771,000</t>
+          <t>3,334,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>21,675,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>21,675,000</t>
+          <t>8,771,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1496,139 +1496,139 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,490,218,272</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>6,553,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>44,393,000</t>
+          <t>1,290,477,637</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>17,290,000</t>
+          <t>6,553,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1657,66 +1657,66 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,295,332,971</t>
+          <t>17,290,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-39,053,592</t>
+          <t>-233,397,675</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.18%</t>
         </is>
       </c>
     </row>
